--- a/data/gummibears.xlsx
+++ b/data/gummibears.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10222"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kruppajo/work/GitHub/jkruppa.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC746220-4B75-5443-BE23-AB505042158B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AAA4458-A0A9-CB4D-B24C-F2D72BE5DCFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6580" yWindow="1920" windowWidth="28200" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2960" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2993" uniqueCount="29">
   <si>
     <t>m</t>
   </si>
@@ -641,7 +641,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Q1033"/>
+  <dimension ref="A1:Q1044"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -48201,6 +48201,523 @@
         <v>1</v>
       </c>
     </row>
+    <row r="1034" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1034" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1034" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1034" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1034" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1034" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1034" s="6">
+        <v>4</v>
+      </c>
+      <c r="G1034" s="6">
+        <v>2</v>
+      </c>
+      <c r="H1034" s="6">
+        <v>0</v>
+      </c>
+      <c r="I1034" s="6">
+        <v>9</v>
+      </c>
+      <c r="J1034" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1034" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1034" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1034" s="6">
+        <v>19</v>
+      </c>
+      <c r="N1034" s="6">
+        <v>164</v>
+      </c>
+      <c r="O1034" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1035" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1035" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1035" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1035" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1035" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1035" s="6">
+        <v>1</v>
+      </c>
+      <c r="G1035" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1035" s="6">
+        <v>2</v>
+      </c>
+      <c r="I1035" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1035" s="6">
+        <v>6</v>
+      </c>
+      <c r="K1035" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1035" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1035" s="6">
+        <v>19</v>
+      </c>
+      <c r="N1035" s="6">
+        <v>165</v>
+      </c>
+      <c r="O1035" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1036" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1036" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1036" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1036" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1036" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1036" s="6">
+        <v>4</v>
+      </c>
+      <c r="G1036" s="6">
+        <v>0</v>
+      </c>
+      <c r="H1036" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1036" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1036" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1036" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1036" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1036" s="6">
+        <v>23</v>
+      </c>
+      <c r="N1036" s="6">
+        <v>168</v>
+      </c>
+      <c r="O1036" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1037" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1037" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1037" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1037" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1037" s="6">
+        <v>4</v>
+      </c>
+      <c r="F1037" s="6">
+        <v>2</v>
+      </c>
+      <c r="G1037" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1037" s="6">
+        <v>0</v>
+      </c>
+      <c r="I1037" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1037" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1037" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1037" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1037" s="6">
+        <v>20</v>
+      </c>
+      <c r="N1037" s="6">
+        <v>170</v>
+      </c>
+      <c r="O1037" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1038" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1038" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1038" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1038" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1038" s="6">
+        <v>3</v>
+      </c>
+      <c r="F1038" s="6">
+        <v>3</v>
+      </c>
+      <c r="G1038" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1038" s="6">
+        <v>0</v>
+      </c>
+      <c r="I1038" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1038" s="6">
+        <v>4</v>
+      </c>
+      <c r="K1038" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1038" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1038" s="6">
+        <v>20</v>
+      </c>
+      <c r="N1038" s="6">
+        <v>180</v>
+      </c>
+      <c r="O1038" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1039" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1039" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1039" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1039" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1039" s="6">
+        <v>3</v>
+      </c>
+      <c r="F1039" s="6">
+        <v>1</v>
+      </c>
+      <c r="G1039" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1039" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1039" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1039" s="6">
+        <v>6</v>
+      </c>
+      <c r="K1039" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1039" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1039" s="6">
+        <v>28</v>
+      </c>
+      <c r="N1039" s="6">
+        <v>172</v>
+      </c>
+      <c r="O1039" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1040" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1040" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1040" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1040" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1040" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1040" s="6">
+        <v>2</v>
+      </c>
+      <c r="G1040" s="6">
+        <v>2</v>
+      </c>
+      <c r="H1040" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1040" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1040" s="6">
+        <v>6</v>
+      </c>
+      <c r="K1040" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1040" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1040" s="6">
+        <v>20</v>
+      </c>
+      <c r="N1040" s="6">
+        <v>170</v>
+      </c>
+      <c r="O1040" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1041" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1041" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1041" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1041" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1041" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1041" s="6">
+        <v>1</v>
+      </c>
+      <c r="G1041" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1041" s="6">
+        <v>3</v>
+      </c>
+      <c r="I1041" s="6">
+        <v>11</v>
+      </c>
+      <c r="J1041" s="6">
+        <v>6</v>
+      </c>
+      <c r="K1041" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1041" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1041" s="6">
+        <v>22</v>
+      </c>
+      <c r="N1041" s="6">
+        <v>185</v>
+      </c>
+      <c r="O1041" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1042" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1042" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1042" s="6">
+        <v>2</v>
+      </c>
+      <c r="D1042" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1042" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1042" s="6">
+        <v>1</v>
+      </c>
+      <c r="G1042" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1042" s="6">
+        <v>2</v>
+      </c>
+      <c r="I1042" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1042" s="6">
+        <v>6</v>
+      </c>
+      <c r="K1042" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1042" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1042" s="6">
+        <v>20</v>
+      </c>
+      <c r="N1042" s="6">
+        <v>164</v>
+      </c>
+      <c r="O1042" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1043" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1043" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1043" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1043" s="6">
+        <v>0</v>
+      </c>
+      <c r="E1043" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1043" s="6">
+        <v>1</v>
+      </c>
+      <c r="G1043" s="6">
+        <v>4</v>
+      </c>
+      <c r="H1043" s="6">
+        <v>2</v>
+      </c>
+      <c r="I1043" s="6">
+        <v>9</v>
+      </c>
+      <c r="J1043" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1043" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1043" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1043" s="6">
+        <v>24</v>
+      </c>
+      <c r="N1043" s="6">
+        <v>169</v>
+      </c>
+      <c r="O1043" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1044" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1044" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1044" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1044" s="6">
+        <v>3</v>
+      </c>
+      <c r="E1044" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1044" s="6">
+        <v>1</v>
+      </c>
+      <c r="G1044" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1044" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1044" s="6">
+        <v>7</v>
+      </c>
+      <c r="J1044" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1044" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1044" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1044" s="6">
+        <v>19</v>
+      </c>
+      <c r="N1044" s="6">
+        <v>155</v>
+      </c>
+      <c r="O1044" s="6">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/data/gummibears.xlsx
+++ b/data/gummibears.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kruppajo/work/GitHub/jkruppa.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AAA4458-A0A9-CB4D-B24C-F2D72BE5DCFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C363C8-877B-6040-BFB4-6C56C634A5F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6580" yWindow="1920" windowWidth="28200" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48279,7 +48279,7 @@
       <c r="J1035" s="6">
         <v>6</v>
       </c>
-      <c r="K1035" t="s">
+      <c r="K1035" s="6" t="s">
         <v>2</v>
       </c>
       <c r="L1035" t="s">
@@ -48326,7 +48326,7 @@
       <c r="J1036" s="6">
         <v>4</v>
       </c>
-      <c r="K1036" t="s">
+      <c r="K1036" s="6" t="s">
         <v>2</v>
       </c>
       <c r="L1036" t="s">

--- a/data/gummibears.xlsx
+++ b/data/gummibears.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kruppajo/work/GitHub/jkruppa.github.io/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jokruppa\Documents\GitHub\jkruppa.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C363C8-877B-6040-BFB4-6C56C634A5F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D02ADFA-79E5-40D7-B310-669A804AEF81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6580" yWindow="1920" windowWidth="28200" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="0" windowWidth="30960" windowHeight="16824" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabellenblatt1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2993" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3047" uniqueCount="29">
   <si>
     <t>m</t>
   </si>
@@ -641,21 +641,21 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Q1044"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:Q1068"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="4" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="8.6640625" bestFit="1" customWidth="1"/>
@@ -1609,7 +1609,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="13">
+    <row r="21" spans="1:15" ht="13.2">
       <c r="A21">
         <v>2018</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="13">
+    <row r="22" spans="1:15" ht="13.2">
       <c r="A22">
         <v>2018</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="13">
+    <row r="23" spans="1:15" ht="13.2">
       <c r="A23">
         <v>2018</v>
       </c>
@@ -1753,7 +1753,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="13">
+    <row r="24" spans="1:15" ht="13.2">
       <c r="A24">
         <v>2018</v>
       </c>
@@ -1801,7 +1801,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="13">
+    <row r="25" spans="1:15" ht="13.2">
       <c r="A25">
         <v>2018</v>
       </c>
@@ -1849,7 +1849,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="13">
+    <row r="26" spans="1:15" ht="13.2">
       <c r="A26">
         <v>2018</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="13">
+    <row r="27" spans="1:15" ht="13.2">
       <c r="A27">
         <v>2018</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="13">
+    <row r="28" spans="1:15" ht="13.2">
       <c r="A28">
         <v>2018</v>
       </c>
@@ -1993,7 +1993,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="13">
+    <row r="29" spans="1:15" ht="13.2">
       <c r="A29">
         <v>2018</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="13">
+    <row r="30" spans="1:15" ht="13.2">
       <c r="A30">
         <v>2018</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="13">
+    <row r="31" spans="1:15" ht="13.2">
       <c r="A31">
         <v>2018</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="13">
+    <row r="32" spans="1:15" ht="13.2">
       <c r="A32">
         <v>2018</v>
       </c>
@@ -2173,7 +2173,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="13">
+    <row r="33" spans="1:15" ht="13.2">
       <c r="A33">
         <v>2018</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="13">
+    <row r="34" spans="1:15" ht="13.2">
       <c r="A34">
         <v>2018</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="13">
+    <row r="35" spans="1:15" ht="13.2">
       <c r="A35">
         <v>2018</v>
       </c>
@@ -2317,7 +2317,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="13">
+    <row r="36" spans="1:15" ht="13.2">
       <c r="A36">
         <v>2018</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="13">
+    <row r="37" spans="1:15" ht="13.2">
       <c r="A37">
         <v>2018</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="13">
+    <row r="38" spans="1:15" ht="13.2">
       <c r="A38">
         <v>2018</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="13">
+    <row r="39" spans="1:15" ht="13.2">
       <c r="A39">
         <v>2018</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="13">
+    <row r="40" spans="1:15" ht="13.2">
       <c r="A40">
         <v>2018</v>
       </c>
@@ -2545,7 +2545,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="13">
+    <row r="41" spans="1:15" ht="13.2">
       <c r="A41">
         <v>2018</v>
       </c>
@@ -2593,7 +2593,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="13">
+    <row r="42" spans="1:15" ht="13.2">
       <c r="A42">
         <v>2018</v>
       </c>
@@ -2641,7 +2641,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="13">
+    <row r="43" spans="1:15" ht="13.2">
       <c r="A43">
         <v>2018</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="13">
+    <row r="44" spans="1:15" ht="13.2">
       <c r="A44">
         <v>2018</v>
       </c>
@@ -2737,7 +2737,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="13">
+    <row r="45" spans="1:15" ht="13.2">
       <c r="A45">
         <v>2018</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="13">
+    <row r="46" spans="1:15" ht="13.2">
       <c r="A46">
         <v>2018</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="13">
+    <row r="47" spans="1:15" ht="13.2">
       <c r="A47">
         <v>2018</v>
       </c>
@@ -2881,7 +2881,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="13">
+    <row r="48" spans="1:15" ht="13.2">
       <c r="A48">
         <v>2018</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="13">
+    <row r="49" spans="1:15" ht="13.2">
       <c r="A49">
         <v>2018</v>
       </c>
@@ -2977,7 +2977,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="13">
+    <row r="50" spans="1:15" ht="13.2">
       <c r="A50">
         <v>2018</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="13">
+    <row r="51" spans="1:15" ht="13.2">
       <c r="A51">
         <v>2018</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="13">
+    <row r="52" spans="1:15" ht="13.2">
       <c r="A52">
         <v>2018</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="13">
+    <row r="53" spans="1:15" ht="13.2">
       <c r="A53">
         <v>2018</v>
       </c>
@@ -3166,7 +3166,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="13">
+    <row r="54" spans="1:15" ht="13.2">
       <c r="A54">
         <v>2018</v>
       </c>
@@ -3214,7 +3214,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="13">
+    <row r="55" spans="1:15" ht="13.2">
       <c r="A55">
         <v>2018</v>
       </c>
@@ -3262,7 +3262,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="13">
+    <row r="56" spans="1:15" ht="13.2">
       <c r="A56">
         <v>2018</v>
       </c>
@@ -3298,7 +3298,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="13">
+    <row r="57" spans="1:15" ht="13.2">
       <c r="A57">
         <v>2018</v>
       </c>
@@ -3346,7 +3346,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="13">
+    <row r="58" spans="1:15" ht="13.2">
       <c r="A58">
         <v>2018</v>
       </c>
@@ -3394,7 +3394,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="13">
+    <row r="59" spans="1:15" ht="13.2">
       <c r="A59">
         <v>2018</v>
       </c>
@@ -3442,7 +3442,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="13">
+    <row r="60" spans="1:15" ht="13.2">
       <c r="A60">
         <v>2018</v>
       </c>
@@ -3490,7 +3490,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="13">
+    <row r="61" spans="1:15" ht="13.2">
       <c r="A61">
         <v>2018</v>
       </c>
@@ -3538,7 +3538,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="13">
+    <row r="62" spans="1:15" ht="13.2">
       <c r="A62">
         <v>2018</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="13">
+    <row r="63" spans="1:15" ht="13.2">
       <c r="A63">
         <v>2018</v>
       </c>
@@ -3631,7 +3631,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="13">
+    <row r="64" spans="1:15" ht="13.2">
       <c r="A64">
         <v>2018</v>
       </c>
@@ -3679,7 +3679,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="13">
+    <row r="65" spans="1:15" ht="13.2">
       <c r="A65">
         <v>2018</v>
       </c>
@@ -3727,7 +3727,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="13">
+    <row r="66" spans="1:15" ht="13.2">
       <c r="A66">
         <v>2018</v>
       </c>
@@ -3775,7 +3775,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:15" ht="13">
+    <row r="67" spans="1:15" ht="13.2">
       <c r="A67">
         <v>2018</v>
       </c>
@@ -3823,7 +3823,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:15" ht="13">
+    <row r="68" spans="1:15" ht="13.2">
       <c r="A68">
         <v>2018</v>
       </c>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L68" s="1"/>
     </row>
-    <row r="69" spans="1:15" ht="13">
+    <row r="69" spans="1:15" ht="13.2">
       <c r="A69">
         <v>2018</v>
       </c>
@@ -3908,7 +3908,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="13">
+    <row r="70" spans="1:15" ht="13.2">
       <c r="A70">
         <v>2018</v>
       </c>
@@ -3956,7 +3956,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:15" ht="13">
+    <row r="71" spans="1:15" ht="13.2">
       <c r="A71">
         <v>2018</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:15" ht="13">
+    <row r="72" spans="1:15" ht="13.2">
       <c r="A72">
         <v>2018</v>
       </c>
@@ -4040,7 +4040,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="73" spans="1:15" ht="13">
+    <row r="73" spans="1:15" ht="13.2">
       <c r="A73">
         <v>2018</v>
       </c>
@@ -4088,7 +4088,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:15" ht="13">
+    <row r="74" spans="1:15" ht="13.2">
       <c r="A74">
         <v>2018</v>
       </c>
@@ -4136,7 +4136,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:15" ht="13">
+    <row r="75" spans="1:15" ht="13.2">
       <c r="A75">
         <v>2018</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:15" ht="14">
+    <row r="77" spans="1:15" ht="13.2">
       <c r="A77">
         <v>2018</v>
       </c>
@@ -4568,7 +4568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:15" ht="14">
+    <row r="84" spans="1:15" ht="13.2">
       <c r="A84">
         <v>2018</v>
       </c>
@@ -48631,43 +48631,43 @@
       <c r="B1043" t="s">
         <v>17</v>
       </c>
-      <c r="C1043" s="6">
-        <v>1</v>
-      </c>
-      <c r="D1043" s="6">
-        <v>0</v>
-      </c>
-      <c r="E1043" s="6">
-        <v>1</v>
-      </c>
-      <c r="F1043" s="6">
-        <v>1</v>
-      </c>
-      <c r="G1043" s="6">
-        <v>4</v>
-      </c>
-      <c r="H1043" s="6">
-        <v>2</v>
-      </c>
-      <c r="I1043" s="6">
+      <c r="C1043">
+        <v>1</v>
+      </c>
+      <c r="D1043">
+        <v>0</v>
+      </c>
+      <c r="E1043">
+        <v>1</v>
+      </c>
+      <c r="F1043">
+        <v>1</v>
+      </c>
+      <c r="G1043">
+        <v>4</v>
+      </c>
+      <c r="H1043">
+        <v>2</v>
+      </c>
+      <c r="I1043">
         <v>9</v>
       </c>
-      <c r="J1043" s="6">
-        <v>5</v>
-      </c>
-      <c r="K1043" s="6" t="s">
+      <c r="J1043">
+        <v>5</v>
+      </c>
+      <c r="K1043" t="s">
         <v>3</v>
       </c>
       <c r="L1043" t="s">
         <v>1</v>
       </c>
-      <c r="M1043" s="6">
+      <c r="M1043">
         <v>24</v>
       </c>
-      <c r="N1043" s="6">
+      <c r="N1043">
         <v>169</v>
       </c>
-      <c r="O1043" s="6">
+      <c r="O1043">
         <v>2</v>
       </c>
     </row>
@@ -48678,45 +48678,1001 @@
       <c r="B1044" t="s">
         <v>17</v>
       </c>
-      <c r="C1044" s="6">
-        <v>0</v>
-      </c>
-      <c r="D1044" s="6">
-        <v>3</v>
-      </c>
-      <c r="E1044" s="6">
-        <v>1</v>
-      </c>
-      <c r="F1044" s="6">
-        <v>1</v>
-      </c>
-      <c r="G1044" s="6">
-        <v>1</v>
-      </c>
-      <c r="H1044" s="6">
-        <v>1</v>
-      </c>
-      <c r="I1044" s="6">
+      <c r="C1044">
+        <v>0</v>
+      </c>
+      <c r="D1044">
+        <v>3</v>
+      </c>
+      <c r="E1044">
+        <v>1</v>
+      </c>
+      <c r="F1044">
+        <v>1</v>
+      </c>
+      <c r="G1044">
+        <v>1</v>
+      </c>
+      <c r="H1044">
+        <v>1</v>
+      </c>
+      <c r="I1044">
         <v>7</v>
       </c>
-      <c r="J1044" s="6">
-        <v>5</v>
-      </c>
-      <c r="K1044" s="6" t="s">
+      <c r="J1044">
+        <v>5</v>
+      </c>
+      <c r="K1044" t="s">
         <v>4</v>
       </c>
       <c r="L1044" t="s">
         <v>1</v>
       </c>
-      <c r="M1044" s="6">
+      <c r="M1044">
         <v>19</v>
       </c>
-      <c r="N1044" s="6">
+      <c r="N1044">
         <v>155</v>
       </c>
-      <c r="O1044" s="6">
-        <v>2</v>
-      </c>
+      <c r="O1044">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1045" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1045" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1045">
+        <v>4</v>
+      </c>
+      <c r="D1045">
+        <v>1</v>
+      </c>
+      <c r="E1045">
+        <v>1</v>
+      </c>
+      <c r="F1045">
+        <v>1</v>
+      </c>
+      <c r="G1045">
+        <v>1</v>
+      </c>
+      <c r="H1045">
+        <v>0</v>
+      </c>
+      <c r="I1045">
+        <v>8</v>
+      </c>
+      <c r="J1045">
+        <v>5</v>
+      </c>
+      <c r="K1045" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1045" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1045">
+        <v>26</v>
+      </c>
+      <c r="N1045">
+        <v>173</v>
+      </c>
+      <c r="O1045">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1046" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1046" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1046">
+        <v>2</v>
+      </c>
+      <c r="D1046">
+        <v>1</v>
+      </c>
+      <c r="E1046">
+        <v>2</v>
+      </c>
+      <c r="F1046">
+        <v>1</v>
+      </c>
+      <c r="G1046">
+        <v>1</v>
+      </c>
+      <c r="H1046">
+        <v>1</v>
+      </c>
+      <c r="I1046">
+        <v>8</v>
+      </c>
+      <c r="J1046">
+        <v>6</v>
+      </c>
+      <c r="K1046" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1046" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1046">
+        <v>26</v>
+      </c>
+      <c r="N1046">
+        <v>186</v>
+      </c>
+      <c r="O1046">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1047" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1047" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1047">
+        <v>2</v>
+      </c>
+      <c r="D1047">
+        <v>0</v>
+      </c>
+      <c r="E1047">
+        <v>3</v>
+      </c>
+      <c r="F1047">
+        <v>1</v>
+      </c>
+      <c r="G1047">
+        <v>2</v>
+      </c>
+      <c r="H1047">
+        <v>2</v>
+      </c>
+      <c r="I1047">
+        <v>10</v>
+      </c>
+      <c r="J1047">
+        <v>5</v>
+      </c>
+      <c r="K1047" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1047" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1047">
+        <v>25</v>
+      </c>
+      <c r="N1047">
+        <v>178</v>
+      </c>
+      <c r="O1047">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1048" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1048" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1048">
+        <v>0</v>
+      </c>
+      <c r="D1048">
+        <v>1</v>
+      </c>
+      <c r="E1048">
+        <v>2</v>
+      </c>
+      <c r="F1048">
+        <v>1</v>
+      </c>
+      <c r="G1048">
+        <v>2</v>
+      </c>
+      <c r="H1048">
+        <v>2</v>
+      </c>
+      <c r="I1048">
+        <v>8</v>
+      </c>
+      <c r="J1048">
+        <v>5</v>
+      </c>
+      <c r="K1048" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1048" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1048">
+        <v>24</v>
+      </c>
+      <c r="N1048">
+        <v>182</v>
+      </c>
+      <c r="O1048">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1049" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1049" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1049">
+        <v>1</v>
+      </c>
+      <c r="D1049">
+        <v>1</v>
+      </c>
+      <c r="E1049">
+        <v>1</v>
+      </c>
+      <c r="F1049">
+        <v>4</v>
+      </c>
+      <c r="G1049">
+        <v>1</v>
+      </c>
+      <c r="H1049">
+        <v>0</v>
+      </c>
+      <c r="I1049">
+        <v>8</v>
+      </c>
+      <c r="J1049">
+        <v>5</v>
+      </c>
+      <c r="K1049" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1049" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1049">
+        <v>24</v>
+      </c>
+      <c r="N1049">
+        <v>180</v>
+      </c>
+      <c r="O1049">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1050" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1050" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1050">
+        <v>1</v>
+      </c>
+      <c r="D1050">
+        <v>2</v>
+      </c>
+      <c r="E1050">
+        <v>1</v>
+      </c>
+      <c r="F1050">
+        <v>2</v>
+      </c>
+      <c r="G1050">
+        <v>2</v>
+      </c>
+      <c r="H1050">
+        <v>1</v>
+      </c>
+      <c r="I1050">
+        <v>9</v>
+      </c>
+      <c r="J1050">
+        <v>6</v>
+      </c>
+      <c r="K1050" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1050" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1050">
+        <v>27</v>
+      </c>
+      <c r="N1050">
+        <v>185</v>
+      </c>
+      <c r="O1050">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1051" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1051" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1051">
+        <v>3</v>
+      </c>
+      <c r="D1051">
+        <v>2</v>
+      </c>
+      <c r="E1051">
+        <v>0</v>
+      </c>
+      <c r="F1051">
+        <v>0</v>
+      </c>
+      <c r="G1051">
+        <v>0</v>
+      </c>
+      <c r="H1051">
+        <v>3</v>
+      </c>
+      <c r="I1051">
+        <v>8</v>
+      </c>
+      <c r="J1051">
+        <v>3</v>
+      </c>
+      <c r="K1051" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1051" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1051">
+        <v>27</v>
+      </c>
+      <c r="N1051">
+        <v>176</v>
+      </c>
+      <c r="O1051">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1052" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1052" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1052">
+        <v>1</v>
+      </c>
+      <c r="D1052">
+        <v>0</v>
+      </c>
+      <c r="E1052">
+        <v>4</v>
+      </c>
+      <c r="F1052">
+        <v>1</v>
+      </c>
+      <c r="G1052">
+        <v>0</v>
+      </c>
+      <c r="H1052">
+        <v>2</v>
+      </c>
+      <c r="I1052">
+        <v>8</v>
+      </c>
+      <c r="J1052">
+        <v>4</v>
+      </c>
+      <c r="K1052" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1052" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1052">
+        <v>25</v>
+      </c>
+      <c r="N1052">
+        <v>178</v>
+      </c>
+      <c r="O1052">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1053" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1053" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1053">
+        <v>1</v>
+      </c>
+      <c r="D1053">
+        <v>2</v>
+      </c>
+      <c r="E1053">
+        <v>4</v>
+      </c>
+      <c r="F1053">
+        <v>2</v>
+      </c>
+      <c r="G1053">
+        <v>0</v>
+      </c>
+      <c r="H1053">
+        <v>0</v>
+      </c>
+      <c r="I1053">
+        <v>9</v>
+      </c>
+      <c r="J1053">
+        <v>4</v>
+      </c>
+      <c r="K1053" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1053" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1053">
+        <v>23</v>
+      </c>
+      <c r="N1053">
+        <v>170</v>
+      </c>
+      <c r="O1053">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1054" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1054" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1054">
+        <v>3</v>
+      </c>
+      <c r="D1054">
+        <v>0</v>
+      </c>
+      <c r="E1054">
+        <v>1</v>
+      </c>
+      <c r="F1054">
+        <v>4</v>
+      </c>
+      <c r="G1054">
+        <v>0</v>
+      </c>
+      <c r="H1054">
+        <v>1</v>
+      </c>
+      <c r="I1054">
+        <v>9</v>
+      </c>
+      <c r="J1054">
+        <v>4</v>
+      </c>
+      <c r="K1054" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1054" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1054">
+        <v>25</v>
+      </c>
+      <c r="N1054">
+        <v>168</v>
+      </c>
+      <c r="O1054">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1055" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1055" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1055">
+        <v>1</v>
+      </c>
+      <c r="D1055">
+        <v>3</v>
+      </c>
+      <c r="E1055">
+        <v>2</v>
+      </c>
+      <c r="F1055">
+        <v>2</v>
+      </c>
+      <c r="G1055">
+        <v>1</v>
+      </c>
+      <c r="H1055">
+        <v>1</v>
+      </c>
+      <c r="I1055">
+        <v>10</v>
+      </c>
+      <c r="J1055">
+        <v>6</v>
+      </c>
+      <c r="K1055" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1055" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1055">
+        <v>28</v>
+      </c>
+      <c r="N1055">
+        <v>163</v>
+      </c>
+      <c r="O1055">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1056" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1056" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1056">
+        <v>0</v>
+      </c>
+      <c r="D1056">
+        <v>0</v>
+      </c>
+      <c r="E1056">
+        <v>3</v>
+      </c>
+      <c r="F1056">
+        <v>1</v>
+      </c>
+      <c r="G1056">
+        <v>3</v>
+      </c>
+      <c r="H1056">
+        <v>1</v>
+      </c>
+      <c r="I1056">
+        <v>8</v>
+      </c>
+      <c r="J1056">
+        <v>4</v>
+      </c>
+      <c r="K1056" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1056" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1056">
+        <v>23</v>
+      </c>
+      <c r="N1056">
+        <v>170</v>
+      </c>
+      <c r="O1056">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A1057" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1057" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1057">
+        <v>2</v>
+      </c>
+      <c r="D1057">
+        <v>2</v>
+      </c>
+      <c r="E1057">
+        <v>1</v>
+      </c>
+      <c r="F1057">
+        <v>2</v>
+      </c>
+      <c r="G1057">
+        <v>0</v>
+      </c>
+      <c r="H1057">
+        <v>1</v>
+      </c>
+      <c r="I1057">
+        <v>8</v>
+      </c>
+      <c r="J1057">
+        <v>5</v>
+      </c>
+      <c r="K1057" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1057" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1057">
+        <v>24</v>
+      </c>
+      <c r="N1057">
+        <v>178</v>
+      </c>
+      <c r="O1057">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A1058" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1058" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1058">
+        <v>3</v>
+      </c>
+      <c r="D1058">
+        <v>1</v>
+      </c>
+      <c r="E1058">
+        <v>1</v>
+      </c>
+      <c r="F1058">
+        <v>2</v>
+      </c>
+      <c r="G1058">
+        <v>1</v>
+      </c>
+      <c r="H1058">
+        <v>0</v>
+      </c>
+      <c r="I1058">
+        <v>8</v>
+      </c>
+      <c r="J1058">
+        <v>5</v>
+      </c>
+      <c r="K1058" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1058" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1058">
+        <v>24</v>
+      </c>
+      <c r="N1058">
+        <v>172</v>
+      </c>
+      <c r="O1058">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A1059" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1059" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1059">
+        <v>1</v>
+      </c>
+      <c r="D1059">
+        <v>0</v>
+      </c>
+      <c r="E1059">
+        <v>2</v>
+      </c>
+      <c r="F1059">
+        <v>2</v>
+      </c>
+      <c r="G1059">
+        <v>1</v>
+      </c>
+      <c r="H1059">
+        <v>4</v>
+      </c>
+      <c r="I1059">
+        <v>10</v>
+      </c>
+      <c r="J1059">
+        <v>5</v>
+      </c>
+      <c r="K1059" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1059" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1059">
+        <v>33</v>
+      </c>
+      <c r="N1059">
+        <v>172</v>
+      </c>
+      <c r="O1059">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A1060" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1060" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1060">
+        <v>0</v>
+      </c>
+      <c r="D1060">
+        <v>2</v>
+      </c>
+      <c r="E1060">
+        <v>2</v>
+      </c>
+      <c r="F1060">
+        <v>1</v>
+      </c>
+      <c r="G1060">
+        <v>2</v>
+      </c>
+      <c r="H1060">
+        <v>1</v>
+      </c>
+      <c r="I1060">
+        <v>8</v>
+      </c>
+      <c r="J1060">
+        <v>5</v>
+      </c>
+      <c r="K1060" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1060" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1060">
+        <v>24</v>
+      </c>
+      <c r="N1060">
+        <v>164</v>
+      </c>
+      <c r="O1060">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A1061" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1061" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1061">
+        <v>2</v>
+      </c>
+      <c r="D1061">
+        <v>0</v>
+      </c>
+      <c r="E1061">
+        <v>4</v>
+      </c>
+      <c r="F1061">
+        <v>0</v>
+      </c>
+      <c r="G1061">
+        <v>1</v>
+      </c>
+      <c r="H1061">
+        <v>2</v>
+      </c>
+      <c r="I1061">
+        <v>9</v>
+      </c>
+      <c r="J1061">
+        <v>4</v>
+      </c>
+      <c r="K1061" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1061" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1061">
+        <v>24</v>
+      </c>
+      <c r="N1061">
+        <v>173</v>
+      </c>
+      <c r="O1061">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A1062" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1062" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1062" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1062" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1062" s="6">
+        <v>0</v>
+      </c>
+      <c r="F1062" s="6">
+        <v>3</v>
+      </c>
+      <c r="G1062" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1062" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1062" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1062" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1062" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1062" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1062" s="6">
+        <v>24</v>
+      </c>
+      <c r="N1062" s="6">
+        <v>160</v>
+      </c>
+      <c r="O1062" s="6">
+        <v>10</v>
+      </c>
+      <c r="P1062" s="6"/>
+      <c r="Q1062" s="6"/>
+    </row>
+    <row r="1063" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B1063" s="6"/>
+      <c r="C1063" s="6"/>
+      <c r="D1063" s="6"/>
+      <c r="E1063" s="6"/>
+      <c r="F1063" s="6"/>
+      <c r="G1063" s="6"/>
+      <c r="H1063" s="6"/>
+      <c r="I1063" s="6"/>
+      <c r="J1063" s="6"/>
+      <c r="K1063" s="6"/>
+      <c r="L1063" s="6"/>
+      <c r="M1063" s="6"/>
+      <c r="N1063" s="6"/>
+      <c r="O1063" s="6"/>
+      <c r="P1063" s="6"/>
+      <c r="Q1063" s="6"/>
+    </row>
+    <row r="1064" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B1064" s="6"/>
+      <c r="C1064" s="6"/>
+      <c r="D1064" s="6"/>
+      <c r="E1064" s="6"/>
+      <c r="F1064" s="6"/>
+      <c r="G1064" s="6"/>
+      <c r="H1064" s="6"/>
+      <c r="I1064" s="6"/>
+      <c r="J1064" s="6"/>
+      <c r="K1064" s="6"/>
+      <c r="L1064" s="6"/>
+      <c r="M1064" s="6"/>
+      <c r="N1064" s="6"/>
+      <c r="O1064" s="6"/>
+      <c r="P1064" s="6"/>
+      <c r="Q1064" s="6"/>
+    </row>
+    <row r="1065" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B1065" s="6"/>
+      <c r="C1065" s="6"/>
+      <c r="D1065" s="6"/>
+      <c r="E1065" s="6"/>
+      <c r="F1065" s="6"/>
+      <c r="G1065" s="6"/>
+      <c r="H1065" s="6"/>
+      <c r="I1065" s="6"/>
+      <c r="J1065" s="6"/>
+      <c r="K1065" s="6"/>
+      <c r="L1065" s="6"/>
+      <c r="M1065" s="6"/>
+      <c r="N1065" s="6"/>
+      <c r="O1065" s="6"/>
+      <c r="P1065" s="6"/>
+      <c r="Q1065" s="6"/>
+    </row>
+    <row r="1066" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B1066" s="6"/>
+      <c r="C1066" s="6"/>
+      <c r="D1066" s="6"/>
+      <c r="E1066" s="6"/>
+      <c r="F1066" s="6"/>
+      <c r="G1066" s="6"/>
+      <c r="H1066" s="6"/>
+      <c r="I1066" s="6"/>
+      <c r="J1066" s="6"/>
+      <c r="K1066" s="6"/>
+      <c r="L1066" s="6"/>
+      <c r="M1066" s="6"/>
+      <c r="N1066" s="6"/>
+      <c r="O1066" s="6"/>
+      <c r="P1066" s="6"/>
+      <c r="Q1066" s="6"/>
+    </row>
+    <row r="1067" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B1067" s="6"/>
+      <c r="C1067" s="6"/>
+      <c r="D1067" s="6"/>
+      <c r="E1067" s="6"/>
+      <c r="F1067" s="6"/>
+      <c r="G1067" s="6"/>
+      <c r="H1067" s="6"/>
+      <c r="I1067" s="6"/>
+      <c r="J1067" s="6"/>
+      <c r="K1067" s="6"/>
+      <c r="L1067" s="6"/>
+      <c r="M1067" s="6"/>
+      <c r="N1067" s="6"/>
+      <c r="O1067" s="6"/>
+      <c r="P1067" s="6"/>
+      <c r="Q1067" s="6"/>
+    </row>
+    <row r="1068" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B1068" s="6"/>
+      <c r="C1068" s="6"/>
+      <c r="D1068" s="6"/>
+      <c r="E1068" s="6"/>
+      <c r="F1068" s="6"/>
+      <c r="G1068" s="6"/>
+      <c r="H1068" s="6"/>
+      <c r="I1068" s="6"/>
+      <c r="J1068" s="6"/>
+      <c r="K1068" s="6"/>
+      <c r="L1068" s="6"/>
+      <c r="M1068" s="6"/>
+      <c r="N1068" s="6"/>
+      <c r="O1068" s="6"/>
+      <c r="P1068" s="6"/>
+      <c r="Q1068" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/data/gummibears.xlsx
+++ b/data/gummibears.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jokruppa\Documents\GitHub\jkruppa.github.io\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kruppajo/work/GitHub/jkruppa.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D02ADFA-79E5-40D7-B310-669A804AEF81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74446464-45A4-AA4E-B181-143BF6C8634A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="0" windowWidth="30960" windowHeight="16824" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2300" yWindow="600" windowWidth="30960" windowHeight="16820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabellenblatt1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3047" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3068" uniqueCount="30">
   <si>
     <t>m</t>
   </si>
@@ -119,6 +119,9 @@
   </si>
   <si>
     <t>PhD Osnabrück</t>
+  </si>
+  <si>
+    <t>Modellierung_landwirtschaftlicher_Daten</t>
   </si>
 </sst>
 </file>
@@ -641,21 +644,21 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Q1068"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:Q1069"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="4" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="8.6640625" bestFit="1" customWidth="1"/>
@@ -1609,7 +1612,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="13.2">
+    <row r="21" spans="1:15" ht="13">
       <c r="A21">
         <v>2018</v>
       </c>
@@ -1657,7 +1660,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="13.2">
+    <row r="22" spans="1:15" ht="13">
       <c r="A22">
         <v>2018</v>
       </c>
@@ -1705,7 +1708,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="13.2">
+    <row r="23" spans="1:15" ht="13">
       <c r="A23">
         <v>2018</v>
       </c>
@@ -1753,7 +1756,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="13.2">
+    <row r="24" spans="1:15" ht="13">
       <c r="A24">
         <v>2018</v>
       </c>
@@ -1801,7 +1804,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="13.2">
+    <row r="25" spans="1:15" ht="13">
       <c r="A25">
         <v>2018</v>
       </c>
@@ -1849,7 +1852,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="13.2">
+    <row r="26" spans="1:15" ht="13">
       <c r="A26">
         <v>2018</v>
       </c>
@@ -1897,7 +1900,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="13.2">
+    <row r="27" spans="1:15" ht="13">
       <c r="A27">
         <v>2018</v>
       </c>
@@ -1945,7 +1948,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="13.2">
+    <row r="28" spans="1:15" ht="13">
       <c r="A28">
         <v>2018</v>
       </c>
@@ -1993,7 +1996,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="13.2">
+    <row r="29" spans="1:15" ht="13">
       <c r="A29">
         <v>2018</v>
       </c>
@@ -2041,7 +2044,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="13.2">
+    <row r="30" spans="1:15" ht="13">
       <c r="A30">
         <v>2018</v>
       </c>
@@ -2077,7 +2080,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="13.2">
+    <row r="31" spans="1:15" ht="13">
       <c r="A31">
         <v>2018</v>
       </c>
@@ -2125,7 +2128,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="13.2">
+    <row r="32" spans="1:15" ht="13">
       <c r="A32">
         <v>2018</v>
       </c>
@@ -2173,7 +2176,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="13.2">
+    <row r="33" spans="1:15" ht="13">
       <c r="A33">
         <v>2018</v>
       </c>
@@ -2221,7 +2224,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="13.2">
+    <row r="34" spans="1:15" ht="13">
       <c r="A34">
         <v>2018</v>
       </c>
@@ -2269,7 +2272,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="13.2">
+    <row r="35" spans="1:15" ht="13">
       <c r="A35">
         <v>2018</v>
       </c>
@@ -2317,7 +2320,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="13.2">
+    <row r="36" spans="1:15" ht="13">
       <c r="A36">
         <v>2018</v>
       </c>
@@ -2365,7 +2368,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="13.2">
+    <row r="37" spans="1:15" ht="13">
       <c r="A37">
         <v>2018</v>
       </c>
@@ -2413,7 +2416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="13.2">
+    <row r="38" spans="1:15" ht="13">
       <c r="A38">
         <v>2018</v>
       </c>
@@ -2461,7 +2464,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="13.2">
+    <row r="39" spans="1:15" ht="13">
       <c r="A39">
         <v>2018</v>
       </c>
@@ -2509,7 +2512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="13.2">
+    <row r="40" spans="1:15" ht="13">
       <c r="A40">
         <v>2018</v>
       </c>
@@ -2545,7 +2548,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="13.2">
+    <row r="41" spans="1:15" ht="13">
       <c r="A41">
         <v>2018</v>
       </c>
@@ -2593,7 +2596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="13.2">
+    <row r="42" spans="1:15" ht="13">
       <c r="A42">
         <v>2018</v>
       </c>
@@ -2641,7 +2644,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="13.2">
+    <row r="43" spans="1:15" ht="13">
       <c r="A43">
         <v>2018</v>
       </c>
@@ -2689,7 +2692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="13.2">
+    <row r="44" spans="1:15" ht="13">
       <c r="A44">
         <v>2018</v>
       </c>
@@ -2737,7 +2740,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="13.2">
+    <row r="45" spans="1:15" ht="13">
       <c r="A45">
         <v>2018</v>
       </c>
@@ -2785,7 +2788,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="13.2">
+    <row r="46" spans="1:15" ht="13">
       <c r="A46">
         <v>2018</v>
       </c>
@@ -2833,7 +2836,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="13.2">
+    <row r="47" spans="1:15" ht="13">
       <c r="A47">
         <v>2018</v>
       </c>
@@ -2881,7 +2884,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="13.2">
+    <row r="48" spans="1:15" ht="13">
       <c r="A48">
         <v>2018</v>
       </c>
@@ -2929,7 +2932,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="13.2">
+    <row r="49" spans="1:15" ht="13">
       <c r="A49">
         <v>2018</v>
       </c>
@@ -2977,7 +2980,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="13.2">
+    <row r="50" spans="1:15" ht="13">
       <c r="A50">
         <v>2018</v>
       </c>
@@ -3025,7 +3028,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="13.2">
+    <row r="51" spans="1:15" ht="13">
       <c r="A51">
         <v>2018</v>
       </c>
@@ -3073,7 +3076,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="13.2">
+    <row r="52" spans="1:15" ht="13">
       <c r="A52">
         <v>2018</v>
       </c>
@@ -3118,7 +3121,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="13.2">
+    <row r="53" spans="1:15" ht="13">
       <c r="A53">
         <v>2018</v>
       </c>
@@ -3166,7 +3169,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="13.2">
+    <row r="54" spans="1:15" ht="13">
       <c r="A54">
         <v>2018</v>
       </c>
@@ -3214,7 +3217,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="13.2">
+    <row r="55" spans="1:15" ht="13">
       <c r="A55">
         <v>2018</v>
       </c>
@@ -3262,7 +3265,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="13.2">
+    <row r="56" spans="1:15" ht="13">
       <c r="A56">
         <v>2018</v>
       </c>
@@ -3298,7 +3301,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="13.2">
+    <row r="57" spans="1:15" ht="13">
       <c r="A57">
         <v>2018</v>
       </c>
@@ -3346,7 +3349,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="13.2">
+    <row r="58" spans="1:15" ht="13">
       <c r="A58">
         <v>2018</v>
       </c>
@@ -3394,7 +3397,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="13.2">
+    <row r="59" spans="1:15" ht="13">
       <c r="A59">
         <v>2018</v>
       </c>
@@ -3442,7 +3445,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="13.2">
+    <row r="60" spans="1:15" ht="13">
       <c r="A60">
         <v>2018</v>
       </c>
@@ -3490,7 +3493,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="13.2">
+    <row r="61" spans="1:15" ht="13">
       <c r="A61">
         <v>2018</v>
       </c>
@@ -3538,7 +3541,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="13.2">
+    <row r="62" spans="1:15" ht="13">
       <c r="A62">
         <v>2018</v>
       </c>
@@ -3583,7 +3586,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="13.2">
+    <row r="63" spans="1:15" ht="13">
       <c r="A63">
         <v>2018</v>
       </c>
@@ -3631,7 +3634,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="13.2">
+    <row r="64" spans="1:15" ht="13">
       <c r="A64">
         <v>2018</v>
       </c>
@@ -3679,7 +3682,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="13.2">
+    <row r="65" spans="1:15" ht="13">
       <c r="A65">
         <v>2018</v>
       </c>
@@ -3727,7 +3730,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="13.2">
+    <row r="66" spans="1:15" ht="13">
       <c r="A66">
         <v>2018</v>
       </c>
@@ -3775,7 +3778,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:15" ht="13.2">
+    <row r="67" spans="1:15" ht="13">
       <c r="A67">
         <v>2018</v>
       </c>
@@ -3823,7 +3826,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:15" ht="13.2">
+    <row r="68" spans="1:15" ht="13">
       <c r="A68">
         <v>2018</v>
       </c>
@@ -3860,7 +3863,7 @@
       </c>
       <c r="L68" s="1"/>
     </row>
-    <row r="69" spans="1:15" ht="13.2">
+    <row r="69" spans="1:15" ht="13">
       <c r="A69">
         <v>2018</v>
       </c>
@@ -3908,7 +3911,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="13.2">
+    <row r="70" spans="1:15" ht="13">
       <c r="A70">
         <v>2018</v>
       </c>
@@ -3956,7 +3959,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:15" ht="13.2">
+    <row r="71" spans="1:15" ht="13">
       <c r="A71">
         <v>2018</v>
       </c>
@@ -4004,7 +4007,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:15" ht="13.2">
+    <row r="72" spans="1:15" ht="13">
       <c r="A72">
         <v>2018</v>
       </c>
@@ -4040,7 +4043,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="73" spans="1:15" ht="13.2">
+    <row r="73" spans="1:15" ht="13">
       <c r="A73">
         <v>2018</v>
       </c>
@@ -4088,7 +4091,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:15" ht="13.2">
+    <row r="74" spans="1:15" ht="13">
       <c r="A74">
         <v>2018</v>
       </c>
@@ -4136,7 +4139,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:15" ht="13.2">
+    <row r="75" spans="1:15" ht="13">
       <c r="A75">
         <v>2018</v>
       </c>
@@ -4232,7 +4235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:15" ht="13.2">
+    <row r="77" spans="1:15" ht="14">
       <c r="A77">
         <v>2018</v>
       </c>
@@ -4568,7 +4571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:15" ht="13.2">
+    <row r="84" spans="1:15" ht="14">
       <c r="A84">
         <v>2018</v>
       </c>
@@ -49567,112 +49570,345 @@
       <c r="Q1062" s="6"/>
     </row>
     <row r="1063" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B1063" s="6"/>
-      <c r="C1063" s="6"/>
-      <c r="D1063" s="6"/>
-      <c r="E1063" s="6"/>
-      <c r="F1063" s="6"/>
-      <c r="G1063" s="6"/>
-      <c r="H1063" s="6"/>
-      <c r="I1063" s="6"/>
-      <c r="J1063" s="6"/>
-      <c r="K1063" s="6"/>
-      <c r="L1063" s="6"/>
-      <c r="M1063" s="6"/>
-      <c r="N1063" s="6"/>
-      <c r="O1063" s="6"/>
+      <c r="A1063" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1063" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1063" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1063" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1063" s="6">
+        <v>0</v>
+      </c>
+      <c r="F1063" s="6">
+        <v>3</v>
+      </c>
+      <c r="G1063" s="6">
+        <v>2</v>
+      </c>
+      <c r="H1063" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1063" s="6">
+        <v>9</v>
+      </c>
+      <c r="J1063" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1063" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1063" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1063" s="6">
+        <v>20</v>
+      </c>
+      <c r="N1063" s="6">
+        <v>186</v>
+      </c>
+      <c r="O1063" s="6">
+        <v>2</v>
+      </c>
       <c r="P1063" s="6"/>
       <c r="Q1063" s="6"/>
     </row>
     <row r="1064" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B1064" s="6"/>
-      <c r="C1064" s="6"/>
-      <c r="D1064" s="6"/>
-      <c r="E1064" s="6"/>
-      <c r="F1064" s="6"/>
-      <c r="G1064" s="6"/>
-      <c r="H1064" s="6"/>
-      <c r="I1064" s="6"/>
-      <c r="J1064" s="6"/>
-      <c r="K1064" s="6"/>
-      <c r="L1064" s="6"/>
-      <c r="M1064" s="6"/>
-      <c r="N1064" s="6"/>
-      <c r="O1064" s="6"/>
+      <c r="A1064" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1064" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1064" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1064" s="6">
+        <v>4</v>
+      </c>
+      <c r="E1064" s="6">
+        <v>0</v>
+      </c>
+      <c r="F1064" s="6">
+        <v>1</v>
+      </c>
+      <c r="G1064" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1064" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1064" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1064" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1064" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1064" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1064" s="6">
+        <v>24</v>
+      </c>
+      <c r="N1064" s="6">
+        <v>179</v>
+      </c>
+      <c r="O1064" s="6">
+        <v>2</v>
+      </c>
       <c r="P1064" s="6"/>
       <c r="Q1064" s="6"/>
     </row>
     <row r="1065" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B1065" s="6"/>
-      <c r="C1065" s="6"/>
-      <c r="D1065" s="6"/>
-      <c r="E1065" s="6"/>
-      <c r="F1065" s="6"/>
-      <c r="G1065" s="6"/>
-      <c r="H1065" s="6"/>
-      <c r="I1065" s="6"/>
-      <c r="J1065" s="6"/>
-      <c r="K1065" s="6"/>
-      <c r="L1065" s="6"/>
-      <c r="M1065" s="6"/>
-      <c r="N1065" s="6"/>
-      <c r="O1065" s="6"/>
+      <c r="A1065" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1065" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1065" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1065" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1065" s="6">
+        <v>0</v>
+      </c>
+      <c r="F1065" s="6">
+        <v>1</v>
+      </c>
+      <c r="G1065" s="6">
+        <v>2</v>
+      </c>
+      <c r="H1065" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1065" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1065" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1065" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1065" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1065" s="6">
+        <v>23</v>
+      </c>
+      <c r="N1065" s="6">
+        <v>183</v>
+      </c>
+      <c r="O1065" s="6">
+        <v>2</v>
+      </c>
       <c r="P1065" s="6"/>
       <c r="Q1065" s="6"/>
     </row>
     <row r="1066" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B1066" s="6"/>
-      <c r="C1066" s="6"/>
-      <c r="D1066" s="6"/>
-      <c r="E1066" s="6"/>
-      <c r="F1066" s="6"/>
-      <c r="G1066" s="6"/>
-      <c r="H1066" s="6"/>
-      <c r="I1066" s="6"/>
-      <c r="J1066" s="6"/>
-      <c r="K1066" s="6"/>
-      <c r="L1066" s="6"/>
-      <c r="M1066" s="6"/>
-      <c r="N1066" s="6"/>
-      <c r="O1066" s="6"/>
+      <c r="A1066" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1066" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1066" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1066" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1066" s="6">
+        <v>2</v>
+      </c>
+      <c r="F1066" s="6">
+        <v>3</v>
+      </c>
+      <c r="G1066" s="6">
+        <v>1</v>
+      </c>
+      <c r="H1066" s="6">
+        <v>0</v>
+      </c>
+      <c r="I1066" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1066" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1066" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1066" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1066" s="6">
+        <v>20</v>
+      </c>
+      <c r="N1066" s="6">
+        <v>178</v>
+      </c>
+      <c r="O1066" s="6">
+        <v>2</v>
+      </c>
       <c r="P1066" s="6"/>
       <c r="Q1066" s="6"/>
     </row>
     <row r="1067" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B1067" s="6"/>
-      <c r="C1067" s="6"/>
-      <c r="D1067" s="6"/>
-      <c r="E1067" s="6"/>
-      <c r="F1067" s="6"/>
-      <c r="G1067" s="6"/>
-      <c r="H1067" s="6"/>
-      <c r="I1067" s="6"/>
-      <c r="J1067" s="6"/>
-      <c r="K1067" s="6"/>
-      <c r="L1067" s="6"/>
-      <c r="M1067" s="6"/>
-      <c r="N1067" s="6"/>
-      <c r="O1067" s="6"/>
+      <c r="A1067" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1067" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1067" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1067" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1067" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1067" s="6">
+        <v>2</v>
+      </c>
+      <c r="G1067" s="6">
+        <v>3</v>
+      </c>
+      <c r="H1067" s="6">
+        <v>0</v>
+      </c>
+      <c r="I1067" s="6">
+        <v>9</v>
+      </c>
+      <c r="J1067" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1067" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1067" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1067" s="6">
+        <v>18</v>
+      </c>
+      <c r="N1067" s="6">
+        <v>158</v>
+      </c>
+      <c r="O1067" s="6">
+        <v>2</v>
+      </c>
       <c r="P1067" s="6"/>
       <c r="Q1067" s="6"/>
     </row>
     <row r="1068" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B1068" s="6"/>
-      <c r="C1068" s="6"/>
-      <c r="D1068" s="6"/>
-      <c r="E1068" s="6"/>
-      <c r="F1068" s="6"/>
-      <c r="G1068" s="6"/>
-      <c r="H1068" s="6"/>
-      <c r="I1068" s="6"/>
-      <c r="J1068" s="6"/>
-      <c r="K1068" s="6"/>
-      <c r="L1068" s="6"/>
-      <c r="M1068" s="6"/>
-      <c r="N1068" s="6"/>
-      <c r="O1068" s="6"/>
+      <c r="A1068" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1068" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1068" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1068" s="6">
+        <v>3</v>
+      </c>
+      <c r="E1068" s="6">
+        <v>2</v>
+      </c>
+      <c r="F1068" s="6">
+        <v>1</v>
+      </c>
+      <c r="G1068" s="6">
+        <v>0</v>
+      </c>
+      <c r="H1068" s="6">
+        <v>1</v>
+      </c>
+      <c r="I1068" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1068" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1068" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1068" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1068" s="6">
+        <v>19</v>
+      </c>
+      <c r="N1068" s="6">
+        <v>194</v>
+      </c>
+      <c r="O1068" s="6">
+        <v>2</v>
+      </c>
       <c r="P1068" s="6"/>
       <c r="Q1068" s="6"/>
+    </row>
+    <row r="1069" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A1069" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B1069" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1069" s="6">
+        <v>0</v>
+      </c>
+      <c r="D1069" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1069" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1069" s="6">
+        <v>2</v>
+      </c>
+      <c r="G1069" s="6">
+        <v>4</v>
+      </c>
+      <c r="H1069" s="6">
+        <v>0</v>
+      </c>
+      <c r="I1069" s="6">
+        <v>8</v>
+      </c>
+      <c r="J1069" s="6">
+        <v>5</v>
+      </c>
+      <c r="K1069" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1069" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1069" s="6">
+        <v>22</v>
+      </c>
+      <c r="N1069" s="6">
+        <v>183</v>
+      </c>
+      <c r="O1069" s="6">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
